--- a/output/pdf_financials_xlsx/STNG.xlsx
+++ b/output/pdf_financials_xlsx/STNG.xlsx
@@ -2227,16 +2227,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.191109</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.191109</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.217609</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.255936</v>
       </c>
     </row>
     <row r="93">
@@ -3582,7 +3582,11 @@
           <t>Reserve (note 11)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3722,7 +3726,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3984,7 +3992,11 @@
           <t>Reserve (note 10)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.191109</v>
       </c>

--- a/output/pdf_financials_xlsx/STNG.xlsx
+++ b/output/pdf_financials_xlsx/STNG.xlsx
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.091778</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.07900600000000001</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.56708</v>
+        <v>-2.475302</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.083275</v>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.091778</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.07900600000000001</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.336401</v>
       </c>
     </row>
     <row r="113">
@@ -4546,7 +4546,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4954,7 +4958,11 @@
           <t>Depreciation on property and equipment</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.091778</v>
       </c>
@@ -6102,7 +6110,11 @@
           <t>Depreciation on property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>0.091778</v>
       </c>

--- a/output/pdf_financials_xlsx/STNG.xlsx
+++ b/output/pdf_financials_xlsx/STNG.xlsx
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.002025</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.022654</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.011391</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.01313</v>
       </c>
     </row>
     <row r="65">
@@ -1728,16 +1728,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.06740500000000001</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.057885</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.057038</v>
       </c>
     </row>
     <row r="68">
@@ -2666,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.066766</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.1358</v>
       </c>
     </row>
     <row r="116">
@@ -4586,7 +4586,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
